--- a/static/data/exports/Retro_DL_AE_2015.xlsx
+++ b/static/data/exports/Retro_DL_AE_2015.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2014,11 +2014,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E22" t="n">
         <v>250</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P177" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P188" t="n">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P196" t="n">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -16585,7 +16585,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16810,7 +16810,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17710,7 +17710,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -17847,7 +17847,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18297,7 +18297,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -18447,7 +18447,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18470,20 +18470,20 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1500623</v>
+        <v>1500622</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Tariq Mirza</t>
+          <t>Moazam Khan</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>HCP</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>16238</v>
+        <v>16362</v>
       </c>
       <c r="E245" t="n">
         <v>19</v>
@@ -18507,12 +18507,12 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Tariq Mirza</t>
+          <t>Moazam Khan</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>RPI(A)</t>
+          <t>HCP</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18522,11 +18522,11 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q245" t="b">
         <v>0</v>
@@ -18545,20 +18545,20 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1500622</v>
+        <v>1500623</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Moazam Khan</t>
+          <t>Tariq Mirza</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>HCP</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>16362</v>
+        <v>16238</v>
       </c>
       <c r="E246" t="n">
         <v>19</v>
@@ -18582,12 +18582,12 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Moazam Khan</t>
+          <t>Tariq Mirza</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>HCP</t>
+          <t>RPI(A)</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18597,11 +18597,11 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q246" t="b">
         <v>0</v>
@@ -18672,7 +18672,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -18897,7 +18897,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -19109,7 +19109,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19409,7 +19409,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P258" t="n">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -19859,7 +19859,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20071,7 +20071,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20221,7 +20221,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20371,7 +20371,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20446,7 +20446,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20521,7 +20521,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -20746,7 +20746,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -21033,7 +21033,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21183,7 +21183,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21258,7 +21258,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21545,7 +21545,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P287" t="n">
@@ -21695,7 +21695,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22207,7 +22207,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22719,7 +22719,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -22869,7 +22869,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -23169,7 +23169,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -23244,7 +23244,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23319,7 +23319,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23681,7 +23681,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -23831,7 +23831,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24193,7 +24193,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24418,7 +24418,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24493,7 +24493,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P330" t="n">
@@ -24855,7 +24855,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -24930,7 +24930,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P332" t="n">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -25230,7 +25230,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P337" t="n">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25455,7 +25455,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P340" t="n">
@@ -25667,7 +25667,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -25817,7 +25817,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P345" t="n">
@@ -25967,7 +25967,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P347" t="n">
@@ -26117,7 +26117,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P348" t="n">
@@ -26192,7 +26192,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26329,7 +26329,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P351" t="n">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26479,7 +26479,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26554,7 +26554,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -26629,7 +26629,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P355" t="n">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -26929,7 +26929,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P359" t="n">
@@ -27004,7 +27004,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -27173,11 +27173,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E363" t="n">
         <v>264</v>
@@ -27216,7 +27216,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -27291,7 +27291,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -27366,7 +27366,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P365" t="n">
@@ -27441,7 +27441,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -27516,7 +27516,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P368" t="n">
@@ -27666,7 +27666,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P369" t="n">
@@ -27741,7 +27741,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P372" t="n">
@@ -27966,7 +27966,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -28041,7 +28041,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P375" t="n">
@@ -28253,7 +28253,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P377" t="n">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P378" t="n">
@@ -28403,7 +28403,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P379" t="n">
@@ -28478,7 +28478,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P380" t="n">
@@ -28553,7 +28553,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P381" t="n">
@@ -28628,7 +28628,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P383" t="n">
@@ -28778,7 +28778,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P384" t="n">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -28928,7 +28928,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P386" t="n">
@@ -29003,7 +29003,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P387" t="n">
@@ -29078,7 +29078,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -29153,7 +29153,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P389" t="n">
@@ -29228,7 +29228,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P390" t="n">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P391" t="n">
@@ -29440,7 +29440,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P393" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P394" t="n">
@@ -29590,7 +29590,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P395" t="n">
@@ -29665,7 +29665,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P396" t="n">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P397" t="n">
@@ -29815,7 +29815,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P398" t="n">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P399" t="n">
@@ -29965,7 +29965,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P400" t="n">
@@ -30040,7 +30040,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P401" t="n">
@@ -30115,7 +30115,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P402" t="n">
@@ -30190,7 +30190,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P403" t="n">
@@ -30265,7 +30265,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P404" t="n">
@@ -30340,7 +30340,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P405" t="n">
@@ -30477,7 +30477,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P407" t="n">
@@ -30552,7 +30552,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P408" t="n">
@@ -30627,7 +30627,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -30702,7 +30702,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P410" t="n">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P411" t="n">
@@ -30852,7 +30852,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -30989,7 +30989,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P414" t="n">
@@ -31064,7 +31064,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P416" t="n">
@@ -31214,7 +31214,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P417" t="n">
@@ -31289,7 +31289,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P418" t="n">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P419" t="n">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P420" t="n">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -31651,7 +31651,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P423" t="n">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P424" t="n">
@@ -31801,7 +31801,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P425" t="n">
@@ -31876,7 +31876,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P426" t="n">
@@ -31951,7 +31951,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P427" t="n">
@@ -32026,7 +32026,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P428" t="n">
@@ -32101,7 +32101,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P429" t="n">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P430" t="n">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P431" t="n">
@@ -32326,7 +32326,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P432" t="n">
@@ -32463,7 +32463,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P434" t="n">
@@ -32538,7 +32538,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P435" t="n">
@@ -32613,7 +32613,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P436" t="n">
@@ -32688,7 +32688,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P437" t="n">
@@ -32763,7 +32763,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P438" t="n">
@@ -32838,7 +32838,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P439" t="n">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P440" t="n">
@@ -32988,7 +32988,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P441" t="n">
@@ -33063,7 +33063,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P442" t="n">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P444" t="n">
@@ -33275,7 +33275,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P445" t="n">
@@ -33350,7 +33350,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P446" t="n">
@@ -33425,7 +33425,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P447" t="n">
@@ -33500,7 +33500,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P448" t="n">
@@ -33575,7 +33575,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P449" t="n">
@@ -33650,7 +33650,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P450" t="n">
@@ -33673,20 +33673,20 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>1500829</v>
+        <v>1500828</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Ajit</t>
+          <t>Sandeep Srivastava</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>GAAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>16356</v>
+        <v>16208</v>
       </c>
       <c r="E451" t="n">
         <v>34</v>
@@ -33710,12 +33710,12 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>Ajit</t>
+          <t>Sandeep Srivastava</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>GAAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -33725,11 +33725,11 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P451" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="Q451" t="b">
         <v>0</v>
@@ -33748,20 +33748,20 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>1500828</v>
+        <v>1500829</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Sandeep Srivastava</t>
+          <t>Ajit</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>GAAP</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>16208</v>
+        <v>16356</v>
       </c>
       <c r="E452" t="n">
         <v>34</v>
@@ -33785,12 +33785,12 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Sandeep Srivastava</t>
+          <t>Ajit</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>GAAP</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -33800,11 +33800,11 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P452" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="Q452" t="b">
         <v>0</v>
@@ -33875,7 +33875,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P453" t="n">
@@ -33950,7 +33950,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P454" t="n">
@@ -34025,7 +34025,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P455" t="n">
@@ -34100,7 +34100,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P456" t="n">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P457" t="n">
@@ -34312,7 +34312,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P459" t="n">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P460" t="n">
@@ -34462,7 +34462,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P461" t="n">
@@ -34537,7 +34537,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P462" t="n">
@@ -34612,7 +34612,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P463" t="n">
@@ -34687,7 +34687,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P464" t="n">
@@ -34762,7 +34762,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P465" t="n">
@@ -34837,7 +34837,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P466" t="n">
@@ -34974,7 +34974,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -35049,7 +35049,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P469" t="n">
@@ -35124,7 +35124,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P470" t="n">
@@ -35199,7 +35199,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P471" t="n">
@@ -35274,7 +35274,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P472" t="n">
@@ -35349,7 +35349,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P473" t="n">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P475" t="n">
@@ -35561,7 +35561,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P476" t="n">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P477" t="n">
@@ -35711,7 +35711,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P478" t="n">
@@ -35786,7 +35786,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P479" t="n">
@@ -35923,7 +35923,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P481" t="n">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P482" t="n">
@@ -36073,7 +36073,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P483" t="n">
@@ -36148,7 +36148,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P484" t="n">
@@ -36223,7 +36223,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P485" t="n">
@@ -36298,7 +36298,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P486" t="n">
@@ -36373,7 +36373,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P487" t="n">
@@ -36448,7 +36448,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P488" t="n">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P490" t="n">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P491" t="n">
@@ -36735,7 +36735,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P492" t="n">
@@ -36810,7 +36810,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P493" t="n">
@@ -36885,7 +36885,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P494" t="n">
@@ -36960,7 +36960,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P495" t="n">
@@ -37035,7 +37035,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P496" t="n">
@@ -37110,7 +37110,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P497" t="n">
@@ -37185,7 +37185,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P498" t="n">
@@ -37260,7 +37260,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P499" t="n">
@@ -37335,7 +37335,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P500" t="n">
@@ -37410,7 +37410,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P501" t="n">
@@ -37547,7 +37547,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P503" t="n">
@@ -37622,7 +37622,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P504" t="n">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P505" t="n">
@@ -37772,7 +37772,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P506" t="n">
@@ -37847,7 +37847,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P507" t="n">
@@ -37922,7 +37922,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P508" t="n">
@@ -38059,7 +38059,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P510" t="n">
@@ -38134,7 +38134,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P511" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P512" t="n">
@@ -38284,7 +38284,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P513" t="n">
@@ -38359,7 +38359,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P514" t="n">
@@ -38434,7 +38434,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P515" t="n">
@@ -38509,7 +38509,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P516" t="n">
@@ -38584,7 +38584,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P517" t="n">
@@ -38721,7 +38721,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P519" t="n">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P520" t="n">
@@ -38871,7 +38871,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P521" t="n">
@@ -38946,7 +38946,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P522" t="n">
@@ -39021,7 +39021,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P523" t="n">
@@ -39096,7 +39096,7 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P524" t="n">
@@ -39233,7 +39233,7 @@
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P526" t="n">
@@ -39308,7 +39308,7 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P527" t="n">
@@ -39383,7 +39383,7 @@
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P528" t="n">
@@ -39458,7 +39458,7 @@
       </c>
       <c r="O529" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P529" t="n">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P530" t="n">
@@ -39670,7 +39670,7 @@
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P532" t="n">
@@ -39745,7 +39745,7 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P533" t="n">
@@ -39820,7 +39820,7 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P534" t="n">
@@ -39895,7 +39895,7 @@
       </c>
       <c r="O535" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P535" t="n">
@@ -39970,7 +39970,7 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P536" t="n">
@@ -40045,7 +40045,7 @@
       </c>
       <c r="O537" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P537" t="n">
@@ -40120,7 +40120,7 @@
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P538" t="n">
@@ -40195,7 +40195,7 @@
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P539" t="n">
@@ -40270,7 +40270,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P540" t="n">
@@ -40345,7 +40345,7 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P541" t="n">
@@ -40420,7 +40420,7 @@
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P542" t="n">
@@ -40495,7 +40495,7 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P543" t="n">
@@ -40570,7 +40570,7 @@
       </c>
       <c r="O544" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P544" t="n">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="O546" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P546" t="n">
@@ -40782,7 +40782,7 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P547" t="n">
@@ -40857,7 +40857,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -40932,7 +40932,7 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P549" t="n">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P550" t="n">
@@ -41082,7 +41082,7 @@
       </c>
       <c r="O551" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P551" t="n">
@@ -41157,7 +41157,7 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P552" t="n">
@@ -41232,7 +41232,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P553" t="n">
@@ -41307,7 +41307,7 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P554" t="n">
@@ -41444,7 +41444,7 @@
       </c>
       <c r="O556" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P556" t="n">
@@ -41519,7 +41519,7 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P557" t="n">
@@ -41594,7 +41594,7 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P558" t="n">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P559" t="n">
@@ -41744,7 +41744,7 @@
       </c>
       <c r="O560" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P560" t="n">
@@ -41881,7 +41881,7 @@
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P562" t="n">
@@ -41956,7 +41956,7 @@
       </c>
       <c r="O563" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P563" t="n">
@@ -42031,7 +42031,7 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P564" t="n">
@@ -42106,7 +42106,7 @@
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P565" t="n">
@@ -42181,7 +42181,7 @@
       </c>
       <c r="O566" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P566" t="n">
@@ -42318,7 +42318,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P568" t="n">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="O569" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P569" t="n">
@@ -42468,7 +42468,7 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P570" t="n">
@@ -42543,7 +42543,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P571" t="n">
@@ -42618,7 +42618,7 @@
       </c>
       <c r="O572" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P572" t="n">
@@ -42693,7 +42693,7 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P573" t="n">
@@ -42768,7 +42768,7 @@
       </c>
       <c r="O574" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P574" t="n">
@@ -42843,7 +42843,7 @@
       </c>
       <c r="O575" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P575" t="n">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P576" t="n">
@@ -42993,7 +42993,7 @@
       </c>
       <c r="O577" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P577" t="n">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P579" t="n">
@@ -43205,7 +43205,7 @@
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P580" t="n">
@@ -43280,7 +43280,7 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P581" t="n">
@@ -43355,7 +43355,7 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P582" t="n">
@@ -43430,7 +43430,7 @@
       </c>
       <c r="O583" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P583" t="n">
@@ -43505,7 +43505,7 @@
       </c>
       <c r="O584" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P584" t="n">
@@ -43580,7 +43580,7 @@
       </c>
       <c r="O585" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P585" t="n">
@@ -43655,7 +43655,7 @@
       </c>
       <c r="O586" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P586" t="n">
@@ -43792,7 +43792,7 @@
       </c>
       <c r="O588" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P588" t="n">
@@ -43867,7 +43867,7 @@
       </c>
       <c r="O589" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P589" t="n">
@@ -43942,7 +43942,7 @@
       </c>
       <c r="O590" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P590" t="n">
@@ -44017,7 +44017,7 @@
       </c>
       <c r="O591" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P591" t="n">
@@ -44092,7 +44092,7 @@
       </c>
       <c r="O592" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P592" t="n">
@@ -44167,7 +44167,7 @@
       </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P593" t="n">
@@ -44242,7 +44242,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P594" t="n">
@@ -44317,7 +44317,7 @@
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P595" t="n">
@@ -44454,7 +44454,7 @@
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P597" t="n">
@@ -44529,7 +44529,7 @@
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P598" t="n">
@@ -44604,7 +44604,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P599" t="n">
@@ -44679,7 +44679,7 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P600" t="n">
@@ -44754,7 +44754,7 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P601" t="n">
@@ -44829,7 +44829,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P602" t="n">
@@ -44904,7 +44904,7 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P603" t="n">
@@ -44979,7 +44979,7 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P604" t="n">
@@ -45116,7 +45116,7 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P606" t="n">
@@ -45191,7 +45191,7 @@
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P607" t="n">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P608" t="n">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P609" t="n">
@@ -45416,7 +45416,7 @@
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P610" t="n">
@@ -45491,7 +45491,7 @@
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P611" t="n">
@@ -45566,7 +45566,7 @@
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P612" t="n">
@@ -45703,7 +45703,7 @@
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P614" t="n">
@@ -45778,7 +45778,7 @@
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P615" t="n">
@@ -45853,7 +45853,7 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P616" t="n">
@@ -45928,7 +45928,7 @@
       </c>
       <c r="O617" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P617" t="n">
@@ -46003,7 +46003,7 @@
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P618" t="n">
@@ -46078,7 +46078,7 @@
       </c>
       <c r="O619" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P619" t="n">
@@ -46153,7 +46153,7 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P620" t="n">
@@ -46290,7 +46290,7 @@
       </c>
       <c r="O622" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P622" t="n">
@@ -46365,7 +46365,7 @@
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P623" t="n">
@@ -46440,7 +46440,7 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P624" t="n">
@@ -46515,7 +46515,7 @@
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P625" t="n">
@@ -46590,7 +46590,7 @@
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P626" t="n">
@@ -46665,7 +46665,7 @@
       </c>
       <c r="O627" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P627" t="n">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P628" t="n">
@@ -46877,7 +46877,7 @@
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P630" t="n">
@@ -46952,7 +46952,7 @@
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P631" t="n">
@@ -47027,7 +47027,7 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P632" t="n">
@@ -47102,7 +47102,7 @@
       </c>
       <c r="O633" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P633" t="n">
@@ -47239,7 +47239,7 @@
       </c>
       <c r="O635" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P635" t="n">
@@ -47314,7 +47314,7 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P636" t="n">
@@ -47389,7 +47389,7 @@
       </c>
       <c r="O637" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P637" t="n">
@@ -47526,7 +47526,7 @@
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P639" t="n">
@@ -47601,7 +47601,7 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P640" t="n">
@@ -47676,7 +47676,7 @@
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P641" t="n">
@@ -47751,7 +47751,7 @@
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P642" t="n">
@@ -47826,7 +47826,7 @@
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P643" t="n">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P644" t="n">
@@ -47976,7 +47976,7 @@
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P645" t="n">
@@ -48051,7 +48051,7 @@
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P646" t="n">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P647" t="n">
@@ -48201,7 +48201,7 @@
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P648" t="n">
@@ -48338,7 +48338,7 @@
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P650" t="n">
@@ -48413,7 +48413,7 @@
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P651" t="n">
@@ -48488,7 +48488,7 @@
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P652" t="n">
@@ -48563,7 +48563,7 @@
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P653" t="n">
@@ -48638,7 +48638,7 @@
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P654" t="n">
@@ -48713,7 +48713,7 @@
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P655" t="n">
@@ -48788,7 +48788,7 @@
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P656" t="n">
@@ -48863,7 +48863,7 @@
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P657" t="n">
@@ -48938,7 +48938,7 @@
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P658" t="n">
@@ -49013,7 +49013,7 @@
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P659" t="n">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P661" t="n">
@@ -49225,7 +49225,7 @@
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P662" t="n">
@@ -49300,7 +49300,7 @@
       </c>
       <c r="O663" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P663" t="n">
@@ -49375,7 +49375,7 @@
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P664" t="n">
@@ -49450,7 +49450,7 @@
       </c>
       <c r="O665" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P665" t="n">
@@ -49525,7 +49525,7 @@
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P666" t="n">
@@ -49600,7 +49600,7 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P667" t="n">
@@ -49675,7 +49675,7 @@
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P668" t="n">
@@ -49750,7 +49750,7 @@
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P669" t="n">
@@ -49887,7 +49887,7 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P671" t="n">
@@ -49962,7 +49962,7 @@
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P672" t="n">
@@ -50037,7 +50037,7 @@
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P673" t="n">
@@ -50112,7 +50112,7 @@
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P674" t="n">
@@ -50187,7 +50187,7 @@
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P675" t="n">
@@ -50262,7 +50262,7 @@
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P676" t="n">
@@ -50399,7 +50399,7 @@
       </c>
       <c r="O678" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P678" t="n">
@@ -50474,7 +50474,7 @@
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P679" t="n">
@@ -50549,7 +50549,7 @@
       </c>
       <c r="O680" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P680" t="n">
@@ -50624,7 +50624,7 @@
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P681" t="n">
@@ -50699,7 +50699,7 @@
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P682" t="n">
@@ -50774,7 +50774,7 @@
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P683" t="n">
@@ -50849,7 +50849,7 @@
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P684" t="n">
@@ -50924,7 +50924,7 @@
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P685" t="n">
@@ -50999,7 +50999,7 @@
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P686" t="n">
@@ -51074,7 +51074,7 @@
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P687" t="n">
@@ -51211,7 +51211,7 @@
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P689" t="n">
@@ -51286,7 +51286,7 @@
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P690" t="n">
@@ -51361,7 +51361,7 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P691" t="n">
@@ -51436,7 +51436,7 @@
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P692" t="n">
@@ -51511,7 +51511,7 @@
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P693" t="n">
@@ -51586,7 +51586,7 @@
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P694" t="n">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P695" t="n">
@@ -51736,7 +51736,7 @@
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P696" t="n">
@@ -51873,7 +51873,7 @@
       </c>
       <c r="O698" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P698" t="n">
@@ -51948,7 +51948,7 @@
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P699" t="n">
@@ -52023,7 +52023,7 @@
       </c>
       <c r="O700" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P700" t="n">
@@ -52098,7 +52098,7 @@
       </c>
       <c r="O701" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P701" t="n">
@@ -52173,7 +52173,7 @@
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P702" t="n">
@@ -52248,7 +52248,7 @@
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P703" t="n">
@@ -52385,7 +52385,7 @@
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P705" t="n">
@@ -52460,7 +52460,7 @@
       </c>
       <c r="O706" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P706" t="n">
@@ -52535,7 +52535,7 @@
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P707" t="n">
@@ -52610,7 +52610,7 @@
       </c>
       <c r="O708" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P708" t="n">
@@ -52685,7 +52685,7 @@
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P709" t="n">
@@ -52760,7 +52760,7 @@
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P710" t="n">
@@ -52897,7 +52897,7 @@
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P712" t="n">
@@ -52972,7 +52972,7 @@
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P713" t="n">
@@ -53047,7 +53047,7 @@
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P714" t="n">
@@ -53122,7 +53122,7 @@
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P715" t="n">
@@ -53197,7 +53197,7 @@
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P716" t="n">
@@ -53272,7 +53272,7 @@
       </c>
       <c r="O717" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P717" t="n">
@@ -53347,7 +53347,7 @@
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P718" t="n">
@@ -53484,7 +53484,7 @@
       </c>
       <c r="O720" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P720" t="n">
@@ -53559,7 +53559,7 @@
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P721" t="n">
@@ -53634,7 +53634,7 @@
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P722" t="n">
@@ -53709,7 +53709,7 @@
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P723" t="n">
@@ -53784,7 +53784,7 @@
       </c>
       <c r="O724" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P724" t="n">
@@ -53859,7 +53859,7 @@
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P725" t="n">
@@ -53996,7 +53996,7 @@
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P727" t="n">
@@ -54071,7 +54071,7 @@
       </c>
       <c r="O728" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P728" t="n">
@@ -54146,7 +54146,7 @@
       </c>
       <c r="O729" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P729" t="n">
@@ -54221,7 +54221,7 @@
       </c>
       <c r="O730" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P730" t="n">
@@ -54296,7 +54296,7 @@
       </c>
       <c r="O731" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P731" t="n">
@@ -54371,7 +54371,7 @@
       </c>
       <c r="O732" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P732" t="n">
@@ -54446,7 +54446,7 @@
       </c>
       <c r="O733" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P733" t="n">
@@ -54521,7 +54521,7 @@
       </c>
       <c r="O734" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P734" t="n">
@@ -54596,7 +54596,7 @@
       </c>
       <c r="O735" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P735" t="n">
@@ -54690,11 +54690,11 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D737" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E737" t="n">
         <v>712</v>
@@ -54733,7 +54733,7 @@
       </c>
       <c r="O737" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P737" t="n">
@@ -54808,7 +54808,7 @@
       </c>
       <c r="O738" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P738" t="n">
@@ -54883,7 +54883,7 @@
       </c>
       <c r="O739" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P739" t="n">
@@ -54958,7 +54958,7 @@
       </c>
       <c r="O740" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P740" t="n">
@@ -55033,7 +55033,7 @@
       </c>
       <c r="O741" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P741" t="n">
@@ -55108,7 +55108,7 @@
       </c>
       <c r="O742" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P742" t="n">
@@ -55183,7 +55183,7 @@
       </c>
       <c r="O743" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P743" t="n">
@@ -55258,7 +55258,7 @@
       </c>
       <c r="O744" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P744" t="n">
